--- a/artfynd/A 31019-2022 artfynd.xlsx
+++ b/artfynd/A 31019-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125105615</v>
+        <v>125106074</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489961</v>
+        <v>489929</v>
       </c>
       <c r="R3" t="n">
-        <v>6835054</v>
+        <v>6835058</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125106074</v>
+        <v>125105615</v>
       </c>
       <c r="B4" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489929</v>
+        <v>489961</v>
       </c>
       <c r="R4" t="n">
-        <v>6835058</v>
+        <v>6835054</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 31019-2022 artfynd.xlsx
+++ b/artfynd/A 31019-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125106074</v>
+        <v>125105615</v>
       </c>
       <c r="B3" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489929</v>
+        <v>489961</v>
       </c>
       <c r="R3" t="n">
-        <v>6835058</v>
+        <v>6835054</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125105615</v>
+        <v>125106074</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489961</v>
+        <v>489929</v>
       </c>
       <c r="R4" t="n">
-        <v>6835054</v>
+        <v>6835058</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 31019-2022 artfynd.xlsx
+++ b/artfynd/A 31019-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125105652</v>
+        <v>125105615</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489959</v>
+        <v>489961</v>
       </c>
       <c r="R2" t="n">
-        <v>6835083</v>
+        <v>6835054</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125105615</v>
+        <v>125105652</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489961</v>
+        <v>489959</v>
       </c>
       <c r="R3" t="n">
-        <v>6835054</v>
+        <v>6835083</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 31019-2022 artfynd.xlsx
+++ b/artfynd/A 31019-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125105615</v>
+        <v>125106074</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489961</v>
+        <v>489929</v>
       </c>
       <c r="R2" t="n">
-        <v>6835054</v>
+        <v>6835058</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125106074</v>
+        <v>125105615</v>
       </c>
       <c r="B4" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489929</v>
+        <v>489961</v>
       </c>
       <c r="R4" t="n">
-        <v>6835058</v>
+        <v>6835054</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 31019-2022 artfynd.xlsx
+++ b/artfynd/A 31019-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125106074</v>
+        <v>125105652</v>
       </c>
       <c r="B2" t="n">
-        <v>91032</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489929</v>
+        <v>489959</v>
       </c>
       <c r="R2" t="n">
-        <v>6835058</v>
+        <v>6835083</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125105652</v>
+        <v>125106074</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489959</v>
+        <v>489929</v>
       </c>
       <c r="R3" t="n">
-        <v>6835083</v>
+        <v>6835058</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>

--- a/artfynd/A 31019-2022 artfynd.xlsx
+++ b/artfynd/A 31019-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125105652</v>
+        <v>125106074</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>91032</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489959</v>
+        <v>489929</v>
       </c>
       <c r="R2" t="n">
-        <v>6835083</v>
+        <v>6835058</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125105615</v>
+        <v>125105652</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489961</v>
+        <v>489959</v>
       </c>
       <c r="R3" t="n">
-        <v>6835054</v>
+        <v>6835083</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125106074</v>
+        <v>125105615</v>
       </c>
       <c r="B4" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489929</v>
+        <v>489961</v>
       </c>
       <c r="R4" t="n">
-        <v>6835058</v>
+        <v>6835054</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 31019-2022 artfynd.xlsx
+++ b/artfynd/A 31019-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125106074</v>
       </c>
       <c r="B2" t="n">
-        <v>91032</v>
+        <v>91186</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125105652</v>
+        <v>125105615</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489959</v>
+        <v>489961</v>
       </c>
       <c r="R3" t="n">
-        <v>6835083</v>
+        <v>6835054</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125105615</v>
+        <v>125105652</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489961</v>
+        <v>489959</v>
       </c>
       <c r="R4" t="n">
-        <v>6835054</v>
+        <v>6835083</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 31019-2022 artfynd.xlsx
+++ b/artfynd/A 31019-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125106074</v>
+        <v>125105615</v>
       </c>
       <c r="B2" t="n">
-        <v>91186</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>489929</v>
+        <v>489961</v>
       </c>
       <c r="R2" t="n">
-        <v>6835058</v>
+        <v>6835054</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125105615</v>
+        <v>125105652</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>489961</v>
+        <v>489959</v>
       </c>
       <c r="R3" t="n">
-        <v>6835054</v>
+        <v>6835083</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125105652</v>
+        <v>125106074</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
+        <v>91186</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489959</v>
+        <v>489929</v>
       </c>
       <c r="R4" t="n">
-        <v>6835083</v>
+        <v>6835058</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
